--- a/output/2026-09-05_08_Italia_Calabria_ATEX_Equipment_Services.xlsx
+++ b/output/2026-09-05_08_Italia_Calabria_ATEX_Equipment_Services.xlsx
@@ -531,7 +531,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Indirizzo: Strada Statale 106 km 245, 88900 Crotone (KR). Stessa ragione sociale/gruppo Strano S.p.A. verificato (vedi filiale RC per dettagli su linea prodotti ATEX aspirazione industriale). Email specifica di filiale non reperita.</t>
+          <t>Indirizzo: Strada Statale 106 km 245, 88900 Crotone (KR). Stessa ragione sociale/gruppo Strano S.p.A. verificato (vedi filiale RC per dettagli su linea prodotti ATEX aspirazione industriale). Email specifica di filiale non reperita. [DUPLICATO — vedi anche: 2026-09-05_08_Italia_Calabria_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Indirizzo: Viale Santuario Madonna di Dipodi, 53, 88040 Feroleto Antico (CZ) - polo/Ce.di Strano confermato da fonte indipendente (reteimprese.it). Stesso gruppo Strano S.p.A. (vedi filiale RC per dettagli su linea prodotti ATEX aspirazione industriale). Email specifica di filiale non reperita.</t>
+          <t>Indirizzo: Viale Santuario Madonna di Dipodi, 53, 88040 Feroleto Antico (CZ) - polo/Ce.di Strano confermato da fonte indipendente (reteimprese.it). Stesso gruppo Strano S.p.A. (vedi filiale RC per dettagli su linea prodotti ATEX aspirazione industriale). Email specifica di filiale non reperita. [DUPLICATO — vedi anche: 2026-09-05_08_Italia_Calabria_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -598,10 +598,9 @@
           <t>ATEX Equipment/Services</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Indirizzo: Via Duca degli Abruzzi, 12, 87036 Rende (CS) - filiale confermata da fonti indipendenti (paginebianche, virgilio, elenchitelefonici) con telefoni pubblici 0984 403692 / 0984 404024 non presenti nella lista grezza originale (aggiunti solo come nota, non confermati come linea diretta della filiale specifica); non essendo presenti nella lista grezza fornita e non potendo confermare con certezza quale sia il numero dedicato a questa sede, il campo telefono è lasciato vuoto per evitare di indovinare. Stesso gruppo Strano S.p.A., stessa linea prodotti ATEX aspirazione industriale del gruppo. Email specifica di filiale non reperita.</t>
+          <t>Indirizzo: Via Duca degli Abruzzi, 12, 87036 Rende (CS) - filiale confermata da fonti indipendenti (paginebianche, virgilio, elenchitelefonici) con telefoni pubblici 0984 403692 / 0984 404024 non presenti nella lista grezza originale (aggiunti solo come nota, non confermati come linea diretta della filiale specifica); non essendo presenti nella lista grezza fornita e non potendo confermare con certezza quale sia il numero dedicato a questa sede, il campo telefono è lasciato vuoto per evitare di indovinare. Stesso gruppo Strano S.p.A., stessa linea prodotti ATEX aspirazione industriale del gruppo. Email specifica di filiale non reperita. [DUPLICATO — vedi anche: 2026-09-05_08_Italia_Calabria_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -675,7 +674,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Indirizzo: Via San Evangelista snc, 87064 Corigliano-Rossano (CS). Stessa ragione sociale/gruppo Garofoli S.p.A. verificato con linea ATEX confermata (vedi filiale Castrovillari).</t>
+          <t>Indirizzo: Via San Evangelista snc, 87064 Corigliano-Rossano (CS). Stessa ragione sociale/gruppo Garofoli S.p.A. verificato con linea ATEX confermata (vedi filiale Castrovillari). [DUPLICATO — vedi anche: 2026-09-05_08_Italia_Calabria_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -712,7 +711,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Indirizzo: Via Ugo Gigli 3, 87064 Corigliano-Rossano (CS). Stessa ragione sociale/gruppo Garofoli S.p.A. verificato con linea ATEX confermata (vedi filiale Castrovillari). Mantenuta separata da filiale Corigliano poiché indirizzo, telefono ed email diversi.</t>
+          <t>Indirizzo: Via Ugo Gigli 3, 87064 Corigliano-Rossano (CS). Stessa ragione sociale/gruppo Garofoli S.p.A. verificato con linea ATEX confermata (vedi filiale Castrovillari). Mantenuta separata da filiale Corigliano poiché indirizzo, telefono ed email diversi. [DUPLICATO — vedi anche: 2026-09-05_08_Italia_Calabria_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
